--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -7573,34 +7573,34 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>5231000</v>
+        <v>4550900</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>25896</v>
+        <v>22529</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>4550970</v>
+        <v>4550900</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>22530</v>
+        <v>22529</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -15886,14 +15886,14 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
         <v>4636200</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>21267</v>
+        <v>21365</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>4636200</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>21267</v>
+        <v>21365</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -22015,12 +22015,12 @@
 (22年-07月-08日)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
-$523万
-$25,896/呎
-(在售)</t>
+$455万
+$22,529/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -22798,7 +22798,7 @@
           <t>G | 339呎 (1房)
 $723万
 $21,334/呎
-(26年-08月-06日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -23168,10 +23168,10 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $464万
-$21,267/呎
-(26年-08月-11日)</t>
+$21,365/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
         <v>4856300</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>22277</v>
+        <v>22379</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>4856300</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>22277</v>
+        <v>22379</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -12099,34 +12099,34 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>8338000</v>
+        <v>7254000</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>24596</v>
+        <v>21398</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>7254060</v>
+        <v>7254000</v>
       </c>
       <c r="L185" s="5" t="n">
         <v>21398</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -22025,10 +22025,10 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $486万
-$22,277/呎
-(26年-08月-12日)</t>
+$22,379/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -22666,12 +22666,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
-$834万
-$24,596/呎
-(在售)</t>
+$725万
+$21,398/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -8503,34 +8503,34 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
-        <v>5215000</v>
+        <v>4537000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>25817</v>
+        <v>22460</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>4537050</v>
+        <v>4537000</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>22461</v>
+        <v>22460</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14951,34 +14951,34 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>5346000</v>
+        <v>4651000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>24523</v>
+        <v>21335</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>4651020</v>
+        <v>4651000</v>
       </c>
       <c r="L231" s="5" t="n">
         <v>21335</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21893,7 +21893,7 @@
           <t>E | 202呎 (开放式)
 $456万
 $22,598/呎
-(26年-08月-28日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -22142,12 +22142,12 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
-$522万
-$25,817/呎
-(在售)</t>
+$454万
+$22,460/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -22901,7 +22901,7 @@
           <t>D | 202呎 (开放式)
 $444万
 $21,974/呎
-(26年-08月-29日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -23039,12 +23039,12 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$535万
-$24,523/呎
-(在售)</t>
+$465万
+$21,335/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -23798,7 +23798,7 @@
           <t>E | 180呎 (开放式)
 $436万
 $24,200/呎
-(26年-08月-31日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4726,14 +4726,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
         <v>4900700</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>22480</v>
+        <v>22584</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>4900700</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>22480</v>
+        <v>22584</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -21644,10 +21644,10 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $490万
-$22,480/呎
-(26年-08月-29日)</t>
+$22,584/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -22020,7 +22020,7 @@
           <t>E | 202呎 (开放式)
 $455万
 $22,529/呎
-(26年-09月-03日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -2861,34 +2861,34 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>5666000</v>
+        <v>4929400</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>25991</v>
+        <v>22612</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4929420</v>
+        <v>4929400</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>22612</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21388,12 +21388,12 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$567万
-$25,991/呎
-(在售)</t>
+$493万
+$22,612/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -20183,38 +20183,30 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H315" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I315" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>6773400</v>
+      </c>
+      <c r="I315" s="5" t="n">
+        <v>31800</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K315" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L315" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K315" s="5" t="n">
+        <v>6773400</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>31800</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -20223,7 +20215,7 @@
       </c>
       <c r="N315" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21024,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23849,12 +23841,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>M | 213呎 (1房)
-招标单位
--
-(在售)</t>
+$677万
+$31,800/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -4845,34 +4845,34 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>5323000</v>
+        <v>4631000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>26351</v>
+        <v>22926</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>4631010</v>
+        <v>4631000</v>
       </c>
       <c r="L68" s="5" t="n">
         <v>22926</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21618,12 +21618,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
-$532万
-$26,351/呎
-(在售)</t>
+$463万
+$22,926/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -5837,34 +5837,34 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>5346000</v>
+        <v>4651000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>26465</v>
+        <v>23025</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>4651020</v>
+        <v>4651000</v>
       </c>
       <c r="L84" s="5" t="n">
         <v>23025</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -14956,14 +14956,14 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
         <v>4651000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>21335</v>
+        <v>21433</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>4651000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>21335</v>
+        <v>21433</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21737,12 +21737,12 @@
 (22年-07月-07日)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
-$535万
-$26,465/呎
-(在售)</t>
+$465万
+$23,025/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -22139,7 +22139,7 @@
           <t>E | 202呎 (开放式)
 $454万
 $22,460/呎
-(26年-09月-11日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -22663,7 +22663,7 @@
           <t>G | 339呎 (1房)
 $725万
 $21,398/呎
-(26年-09月-08日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -23033,10 +23033,10 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $465万
-$21,335/呎
-(26年-09月-13日)</t>
+$21,433/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
         <v>4929400</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>22612</v>
+        <v>22716</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>4929400</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>22612</v>
+        <v>22716</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -4907,34 +4907,34 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>5362000</v>
+        <v>4664900</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>26545</v>
+        <v>23094</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>4664940</v>
+        <v>4664900</v>
       </c>
       <c r="L69" s="5" t="n">
         <v>23094</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21382,10 +21382,10 @@
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $493万
-$22,612/呎
-(26年-09月-17日)</t>
+$22,716/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -21610,12 +21610,12 @@
 (25年-05月-23日)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
-$536万
-$26,545/呎
-(在售)</t>
+$466万
+$23,094/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -23846,7 +23846,7 @@
           <t>M | 213呎 (1房)
 $677万
 $31,800/呎
-(26年-09月-22日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -3791,34 +3791,34 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>5649000</v>
+        <v>4914600</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>25913</v>
+        <v>22544</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>4914630</v>
+        <v>4914600</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>22544</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21507,12 +21507,12 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$565万
-$25,913/呎
-(在售)</t>
+$491万
+$22,544/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -2117,23 +2117,23 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>5410000</v>
+        <v>4706700</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>26782</v>
+        <v>23300</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -3047,34 +3047,34 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>5394000</v>
+        <v>4692700</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>26703</v>
+        <v>23231</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>4692780</v>
+        <v>4692700</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>23232</v>
+        <v>23231</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5842,14 +5842,14 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
         <v>4651000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>23025</v>
+        <v>23139</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>4651000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>23025</v>
+        <v>23139</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -16811,34 +16811,34 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
-        <v>5313000</v>
+        <v>4622300</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>24484</v>
+        <v>21301</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K261" s="5" t="n">
-        <v>4622310</v>
+        <v>4622300</v>
       </c>
       <c r="L261" s="5" t="n">
         <v>21301</v>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21229,12 +21229,12 @@
 (22年-07月-12日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
-$541万
-$26,782/呎
-(在售)</t>
+$471万
+$23,300/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -21356,12 +21356,12 @@
 (22年-07月-07日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
-$539万
-$26,703/呎
-(在售)</t>
+$469万
+$23,231/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -21623,7 +21623,7 @@
           <t>D | 202呎 (开放式)
 $463万
 $22,926/呎
-(26年-09月-24日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -21739,10 +21739,10 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 202呎 (开放式)
+          <t>C | 201呎 (开放式)
 $465万
-$23,025/呎
-(26年-10月-05日)</t>
+$23,139/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -23285,12 +23285,12 @@
 (22年-06月-30日)</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
-$531万
-$24,484/呎
-(在售)</t>
+$462万
+$21,301/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>9356400</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>25425</v>
+        <v>25356</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>9356400</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>25425</v>
+        <v>25356</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>4944200</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>22784</v>
+        <v>22680</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>4944200</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>22784</v>
+        <v>22680</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>4929400</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>22716</v>
+        <v>22612</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>4929400</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>22716</v>
+        <v>22612</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>9382000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>25495</v>
+        <v>25425</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>9382000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>25495</v>
+        <v>25425</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>5243000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>18996</v>
+        <v>19065</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>5243000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>18996</v>
+        <v>19065</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>7909700</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>21494</v>
+        <v>21436</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>7909700</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>21494</v>
+        <v>21436</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>4900700</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>22584</v>
+        <v>22480</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>4900700</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>22584</v>
+        <v>22480</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>5226900</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>18938</v>
+        <v>19007</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>5226900</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>18938</v>
+        <v>19007</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>4651000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>23139</v>
+        <v>23025</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>4651000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>23139</v>
+        <v>23025</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>9207000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>25019</v>
+        <v>24951</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>9207000</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>25019</v>
+        <v>24951</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>4637100</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>23070</v>
+        <v>22956</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>4637100</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>23070</v>
+        <v>22956</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>5795000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>20996</v>
+        <v>21073</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>5795000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>20996</v>
+        <v>21073</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>4856300</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>22379</v>
+        <v>22277</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>4856300</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>22379</v>
+        <v>22277</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>4624000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>23005</v>
+        <v>22891</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>4624000</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>23005</v>
+        <v>22891</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>5777900</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>20934</v>
+        <v>21011</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>5777900</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>20934</v>
+        <v>21011</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>4841500</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>22311</v>
+        <v>22209</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>4841500</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>22311</v>
+        <v>22209</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>5759800</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>20869</v>
+        <v>20945</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>5759800</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>20869</v>
+        <v>20945</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>7044100</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>19142</v>
+        <v>19090</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>7044100</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>19142</v>
+        <v>19090</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>4596200</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>22867</v>
+        <v>22753</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>4596200</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>22867</v>
+        <v>22753</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>6044700</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>21901</v>
+        <v>21981</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>6044700</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>21901</v>
+        <v>21981</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>6878000</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>18690</v>
+        <v>18640</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>6878000</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>18690</v>
+        <v>18640</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>4519600</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>22486</v>
+        <v>22374</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>4519600</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>22486</v>
+        <v>22374</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>6858000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>18636</v>
+        <v>18585</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>6858000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>18636</v>
+        <v>18585</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>4798000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>22111</v>
+        <v>22009</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>4798000</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>22111</v>
+        <v>22009</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>4505700</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>22416</v>
+        <v>22305</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>4505700</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>22416</v>
+        <v>22305</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>6008200</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>21769</v>
+        <v>21848</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>6008200</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>21769</v>
+        <v>21848</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>8027400</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>21814</v>
+        <v>21754</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>8027400</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>21814</v>
+        <v>21754</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>4783200</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>22042</v>
+        <v>21941</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>4783200</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>22042</v>
+        <v>21941</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>4491800</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>22347</v>
+        <v>22237</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>4491800</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>22347</v>
+        <v>22237</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>5887100</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>21330</v>
+        <v>21408</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>5887100</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>21330</v>
+        <v>21408</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>6817200</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>18525</v>
+        <v>18475</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>6817200</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>18525</v>
+        <v>18475</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>4753600</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>21906</v>
+        <v>21806</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>4753600</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>21906</v>
+        <v>21806</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>4464800</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>22213</v>
+        <v>22103</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>4464800</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>22213</v>
+        <v>22103</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>5655300</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>20490</v>
+        <v>20565</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>5655300</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>20490</v>
+        <v>20565</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>6755400</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>18357</v>
+        <v>18307</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>6755400</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>18357</v>
+        <v>18307</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>4409100</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>21936</v>
+        <v>21827</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>4409100</v>
       </c>
       <c r="L219" s="5" t="n">
-        <v>21936</v>
+        <v>21827</v>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>5586000</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>20239</v>
+        <v>20313</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>5586000</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>20239</v>
+        <v>20313</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>6714600</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>18246</v>
+        <v>18197</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>6714600</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>18246</v>
+        <v>18197</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>4651000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>21433</v>
+        <v>21335</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>4651000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>21433</v>
+        <v>21335</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>4368200</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>21732</v>
+        <v>21625</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>4368200</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>21732</v>
+        <v>21625</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>5534700</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>20053</v>
+        <v>20126</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>5534700</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>20053</v>
+        <v>20126</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E244" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>6694600</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>18192</v>
+        <v>18143</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>6694600</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>18192</v>
+        <v>18143</v>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>4636200</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>21365</v>
+        <v>21267</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>4636200</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>21365</v>
+        <v>21267</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>4354300</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>21663</v>
+        <v>21556</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>4354300</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>21663</v>
+        <v>21556</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>5516600</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>19988</v>
+        <v>20060</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>5516600</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>19988</v>
+        <v>20060</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>6673700</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>18135</v>
+        <v>18086</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>6673700</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>18135</v>
+        <v>18086</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>4622300</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>21301</v>
+        <v>21203</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>4622300</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>21301</v>
+        <v>21203</v>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>4340400</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>21594</v>
+        <v>21487</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>4340400</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>21594</v>
+        <v>21487</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>6673700</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>18135</v>
+        <v>18086</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>6673700</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>18135</v>
+        <v>18086</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="E279" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>4340400</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>21594</v>
+        <v>21487</v>
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>4340400</v>
       </c>
       <c r="L279" s="5" t="n">
-        <v>21594</v>
+        <v>21487</v>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="E280" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>5788900</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>20974</v>
+        <v>21051</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>5788900</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>20974</v>
+        <v>21051</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>7567700</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>20564</v>
+        <v>20509</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>7567700</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>20564</v>
+        <v>20509</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>4592700</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>21165</v>
+        <v>21067</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>4592700</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>21165</v>
+        <v>21067</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>4313400</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>21460</v>
+        <v>21353</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>4313400</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>21460</v>
+        <v>21353</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         </is>
       </c>
       <c r="E295" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>5464400</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>19799</v>
+        <v>19871</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>5464400</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>19799</v>
+        <v>19871</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>7743000</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>21041</v>
+        <v>20984</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>7743000</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>21041</v>
+        <v>20984</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>4563100</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>21028</v>
+        <v>20932</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>4563100</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>21028</v>
+        <v>20932</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         </is>
       </c>
       <c r="E309" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>4288200</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>21334</v>
+        <v>21229</v>
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>4288200</v>
       </c>
       <c r="L309" s="5" t="n">
-        <v>21334</v>
+        <v>21229</v>
       </c>
       <c r="M309" s="3" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="E310" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>5707200</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>20678</v>
+        <v>20753</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>5707200</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>20678</v>
+        <v>20753</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
@@ -21255,9 +21255,9 @@
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $494万
-$22,784/呎
+$22,680/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -21271,9 +21271,9 @@
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $936万
-$25,425/呎
+$25,356/呎
 (22年-07月-12日)</t>
         </is>
       </c>
@@ -21382,9 +21382,9 @@
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $493万
-$22,716/呎
+$22,612/呎
 (26年-10月-13日)</t>
         </is>
       </c>
@@ -21477,9 +21477,9 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $524万
-$18,996/呎
+$19,065/呎
 (25年-08月-22日)</t>
         </is>
       </c>
@@ -21512,7 +21512,7 @@
           <t>F | 218呎 (开放式)
 $491万
 $22,544/呎
-(26年-10月-13日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -21525,9 +21525,9 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $938万
-$25,495/呎
+$25,425/呎
 (22年-07月-11日)</t>
         </is>
       </c>
@@ -21604,9 +21604,9 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $523万
-$18,938/呎
+$19,007/呎
 (25年-05月-23日)</t>
         </is>
       </c>
@@ -21636,9 +21636,9 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $490万
-$22,584/呎
+$22,480/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -21652,9 +21652,9 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $791万
-$21,494/呎
+$21,436/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -21739,9 +21739,9 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $465万
-$23,139/呎
+$23,025/呎
 (26年-10月-21日)</t>
         </is>
       </c>
@@ -21858,17 +21858,17 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $580万
-$20,996/呎
+$21,073/呎
 (26年-03月-06日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $464万
-$23,070/呎
+$22,956/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -21906,9 +21906,9 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $921万
-$25,019/呎
+$24,951/呎
 (22年-07月-07日)</t>
         </is>
       </c>
@@ -21985,17 +21985,17 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $578万
-$20,934/呎
+$21,011/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $462万
-$23,005/呎
+$22,891/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -22017,9 +22017,9 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $486万
-$22,379/呎
+$22,277/呎
 (26年-09月-08日)</t>
         </is>
       </c>
@@ -22112,9 +22112,9 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $576万
-$20,869/呎
+$20,945/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -22144,9 +22144,9 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $484万
-$22,311/呎
+$22,209/呎
 (26年-06月-29日)</t>
         </is>
       </c>
@@ -22239,17 +22239,17 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $604万
-$21,901/呎
+$21,981/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $460万
-$22,867/呎
+$22,753/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -22287,9 +22287,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $704万
-$19,142/呎
+$19,090/呎
 (25年-05月-02日)</t>
         </is>
       </c>
@@ -22374,9 +22374,9 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $452万
-$22,486/呎
+$22,374/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -22414,9 +22414,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $688万
-$18,690/呎
+$18,640/呎
 (25年-04月-25日)</t>
         </is>
       </c>
@@ -22493,17 +22493,17 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $601万
-$21,769/呎
+$21,848/呎
 (26年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $451万
-$22,416/呎
+$22,305/呎
 (26年-08月-04日)</t>
         </is>
       </c>
@@ -22525,9 +22525,9 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $480万
-$22,111/呎
+$22,009/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -22541,9 +22541,9 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $686万
-$18,636/呎
+$18,585/呎
 (25年-04月-30日)</t>
         </is>
       </c>
@@ -22620,17 +22620,17 @@
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $589万
-$21,330/呎
+$21,408/呎
 (26年-03月-27日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $449万
-$22,347/呎
+$22,237/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -22652,9 +22652,9 @@
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $478万
-$22,042/呎
+$21,941/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -22668,9 +22668,9 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $803万
-$21,814/呎
+$21,754/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -22747,17 +22747,17 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $566万
-$20,490/呎
+$20,565/呎
 (26年-03月-23日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $446万
-$22,213/呎
+$22,103/呎
 (26年-06月-04日)</t>
         </is>
       </c>
@@ -22779,9 +22779,9 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $475万
-$21,906/呎
+$21,806/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -22795,9 +22795,9 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $682万
-$18,525/呎
+$18,475/呎
 (25年-05月-09日)</t>
         </is>
       </c>
@@ -22874,17 +22874,17 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $559万
-$20,239/呎
+$20,313/呎
 (26年-03月-27日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $441万
-$21,936/呎
+$21,827/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -22922,9 +22922,9 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $676万
-$18,357/呎
+$18,307/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -23001,17 +23001,17 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $553万
-$20,053/呎
+$20,126/呎
 (26年-03月-26日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $437万
-$21,732/呎
+$21,625/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -23033,9 +23033,9 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $465万
-$21,433/呎
+$21,335/呎
 (26年-10月-05日)</t>
         </is>
       </c>
@@ -23049,9 +23049,9 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $671万
-$18,246/呎
+$18,197/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -23128,17 +23128,17 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $552万
-$19,988/呎
+$20,060/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $435万
-$21,663/呎
+$21,556/呎
 (26年-07月-08日)</t>
         </is>
       </c>
@@ -23160,9 +23160,9 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $464万
-$21,365/呎
+$21,267/呎
 (26年-09月-07日)</t>
         </is>
       </c>
@@ -23176,9 +23176,9 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $669万
-$18,192/呎
+$18,143/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -23263,9 +23263,9 @@
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $434万
-$21,594/呎
+$21,487/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -23287,9 +23287,9 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $462万
-$21,301/呎
+$21,203/呎
 (26年-10月-22日)</t>
         </is>
       </c>
@@ -23303,9 +23303,9 @@
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $667万
-$18,135/呎
+$18,086/呎
 (25年-05月-09日)</t>
         </is>
       </c>
@@ -23382,17 +23382,17 @@
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $579万
-$20,974/呎
+$21,051/呎
 (26年-05月-05日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $434万
-$21,594/呎
+$21,487/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -23430,9 +23430,9 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $667万
-$18,135/呎
+$18,086/呎
 (25年-06月-04日)</t>
         </is>
       </c>
@@ -23509,17 +23509,17 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $546万
-$19,799/呎
+$19,871/呎
 (26年-03月-17日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $431万
-$21,460/呎
+$21,353/呎
 (26年-06月-01日)</t>
         </is>
       </c>
@@ -23541,9 +23541,9 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $459万
-$21,165/呎
+$21,067/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -23557,9 +23557,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $757万
-$20,564/呎
+$20,509/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -23636,17 +23636,17 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 276呎 (1房)
+          <t>B | 275呎 (1房)
 $571万
-$20,678/呎
+$20,753/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 201呎 (开放式)
+          <t>C | 202呎 (开放式)
 $429万
-$21,334/呎
+$21,229/呎
 (26年-05月-14日)</t>
         </is>
       </c>
@@ -23668,9 +23668,9 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>F | 217呎 (开放式)
+          <t>F | 218呎 (开放式)
 $456万
-$21,028/呎
+$20,932/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -23684,9 +23684,9 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>H | 368呎 (2房)
+          <t>H | 369呎 (2房)
 $774万
-$21,041/呎
+$20,984/呎
 (26年-05月-14日)</t>
         </is>
       </c>
